--- a/results/lendt_adults.xlsx
+++ b/results/lendt_adults.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,46 +548,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>0.99 [0.99, 1.00]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.99 [0.99, 1.00]</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>0.99 [0.99, 1.00]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.99 [0.99, 1.00]</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,19 +610,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99 [0.98, 0.99]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 1.00]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -626,100 +634,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>540.00 ± 0.00</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>300.00 ± 0.00</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>300.00 ± 0.00</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>540.03 ± 0.17</t>
+          <t>0.98 [0.97, 1.00]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>534.91 ± 30.44</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>539.69 ± 2.58</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>18900</v>
-      </c>
-      <c r="C7" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10500</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>540.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>18901</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>540.03 ± 0.17</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>18722</v>
-      </c>
-      <c r="I7" t="n">
-        <v>18889</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>534.91 ± 30.44</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>539.69 ± 2.58</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>18900</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>10500</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>10500</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>18901</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>18722</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>18889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -740,6 +760,33 @@
         <v>35</v>
       </c>
       <c r="I9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -754,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,42 +854,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
     </row>
@@ -854,37 +901,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.08 [0.00, 0.24]</t>
+          <t>0.08 [0.00, 0.28]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.95]</t>
+          <t>0.90 [0.85, 0.96]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.77 [0.73, 0.81]</t>
+          <t>0.77 [0.72, 0.82]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.43 [0.38, 0.48]</t>
+          <t>0.43 [0.37, 0.49]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.89 [0.85, 0.93]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.35 [0.18, 0.53]</t>
+          <t>0.35 [0.14, 0.56]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.99]</t>
+          <t>0.97 [0.94, 0.99]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -896,234 +943,281 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.30 [0.00, 1.00]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.94]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.85]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.40 [0.34, 0.46]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.90 [0.88, 0.92]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.70 [0.46, 0.93]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.99]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.84 [0.80, 0.88]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.11 [0.00, 0.32]</t>
+          <t>0.30 [0.00, 1.00]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95 [0.90, 1.00]</t>
+          <t>0.90 [0.84, 0.95]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74 [0.69, 0.78]</t>
+          <t>0.81 [0.77, 0.85]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.53 [0.48, 0.57]</t>
+          <t>0.40 [0.33, 0.47]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.93]</t>
+          <t>0.90 [0.87, 0.93]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.32 [0.15, 0.49]</t>
+          <t>0.70 [0.40, 0.99]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 1.00]</t>
+          <t>0.97 [0.94, 0.99]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.96 [0.94, 0.97]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>279.44 ± 177.93</t>
+          <t>0.11 [0.00, 0.37]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1240.03 ± 944.79</t>
+          <t>0.95 [0.89, 1.00]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>377.77 ± 273.61</t>
+          <t>0.74 [0.68, 0.79]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>130.34 ± 95.81</t>
+          <t>0.53 [0.47, 0.58]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>976.83 ± 535.53</t>
+          <t>0.89 [0.85, 0.93]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>65.58 ± 62.45</t>
+          <t>0.32 [0.12, 0.53]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>337.88 ± 296.53</t>
+          <t>0.97 [0.94, 1.00]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>660.93 ± 359.86</t>
+          <t>0.96 [0.94, 0.97]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2515</v>
-      </c>
-      <c r="C7" t="n">
-        <v>43401</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13222</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4562</v>
-      </c>
-      <c r="F7" t="n">
-        <v>34189</v>
-      </c>
-      <c r="G7" t="n">
-        <v>787</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8109</v>
-      </c>
-      <c r="I7" t="n">
-        <v>17845</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>279.44 ± 177.93</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1240.03 ± 944.79</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>377.77 ± 273.61</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>130.34 ± 95.81</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>976.83 ± 535.53</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>65.58 ± 62.45</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>337.88 ± 296.53</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>660.93 ± 359.86</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>2515</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>43401</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>13222</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>4562</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>34189</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>787</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>8109</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>17845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>n_total</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>35</v>
-      </c>
-      <c r="F9" t="n">
-        <v>35</v>
-      </c>
-      <c r="G9" t="n">
-        <v>35</v>
-      </c>
-      <c r="H9" t="n">
-        <v>35</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="B10" t="n">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="n">
         <v>35</v>
       </c>
     </row>

--- a/results/lendt_adults.xlsx
+++ b/results/lendt_adults.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Laboratory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Free-living" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Laboratory matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Free-living" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Free-living matrix" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -724,11 +726,15 @@
       <c r="D8" t="n">
         <v>10500</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
         <v>18901</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" t="n">
         <v>18722</v>
       </c>
@@ -751,11 +757,15 @@
       <c r="D9" t="n">
         <v>35</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" t="n">
         <v>35</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="n">
         <v>35</v>
       </c>
@@ -778,11 +788,15 @@
       <c r="D10" t="n">
         <v>35</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
       <c r="F10" t="n">
         <v>35</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>35</v>
+      </c>
       <c r="H10" t="n">
         <v>35</v>
       </c>
@@ -801,6 +815,1651 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>34.90925925925926</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9974074074074074</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.009728833730787922</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9940654360925615</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0004761904761904762</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.00157793689443717</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.001018230764242453</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.07407407407407408</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.002116402116402117</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.008582487592005968</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.005064589754940576</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>35</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>35</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>35</v>
+      </c>
+      <c r="D31" t="n">
+        <v>35</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>35</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" t="n">
+        <v>35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3933333333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.01123809523809524</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.01437330755676584</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.006300691343303916</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.01617549913288656</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>35</v>
+      </c>
+      <c r="D38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D39" t="n">
+        <v>35</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>34.60666666666667</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9887619047619048</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.01437330755676583</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9838245008671135</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9936993086566962</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>35</v>
+      </c>
+      <c r="D43" t="n">
+        <v>35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>35</v>
+      </c>
+      <c r="D44" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.001851851851851852</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.291005291005291e-05</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0003130200943438951</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0001604362174242179</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>35</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.3185185185185185</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0091005291005291</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.01895121625940376</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.002590558545688552</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.01561049965536965</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>35</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>35</v>
+      </c>
+      <c r="D47" t="n">
+        <v>35</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.006349206349206349</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0375624113212674</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.01925234609090615</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>35</v>
+      </c>
+      <c r="D48" t="n">
+        <v>35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>34.45740740740741</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9844973544973545</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.05186952257698719</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9666795500858688</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1224,4 +2883,2177 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.79294209144394</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9552941515349608</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04935390029809637</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9357703988191506</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.974817904250771</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.002377179080824089</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.804366966015144e-05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0004574883274085783</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0002690200245327411</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2867880116921117</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01062177821081895</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01527115325376229</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.004580711182461005</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0166628452391769</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2941527249784862</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01089454536957356</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01773157653185551</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.003880167308701982</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01790892343044514</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2305299170812718</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.00853814507708414</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01359679625949877</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.003159431615851446</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01391685853831683</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2425087082947844</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.008981804010917941</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01869575412318582</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.001586009998043382</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0163775980237925</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1507013674285818</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005581532126984512</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008919456752059171</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00205311255052231</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.009109951703446712</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3673337928004629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.991031390134529</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8878923766816142</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3329728523295941</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6319467852206908</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.008968609865470852</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0009965122072745391</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002989536621823617</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.003294473478031057</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>23.31858924947201</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9716078853946669</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0683508983184844</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9427458323074687</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.09415630070552564</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.003923179196063568</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.01005499132451292</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.008169029660927578</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>24</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0429198580235382</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.001788327417647425</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.006951760756293604</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004723798537028266</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5443345917989302</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02268060799162209</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0556586835531665</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.04618320882050729</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2632742756435137</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.00752212216124325</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.02140376953333626</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0001696700802074676</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01487457424227903</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>35</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.003296703296703297</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01950355972450423</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.009996410470278194</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.00641025641025641</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0001831501831501832</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.00108353109580579</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0005553561372376773</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.43957851859527</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5268451005312933</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.165324306370006</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4700542143033907</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5836359867591959</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>35</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7789562634995773</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.02225589324284507</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.032933244868577</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01094292781439107</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.03356885867129906</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>35</v>
+      </c>
+      <c r="D31" t="n">
+        <v>35</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4658686401298994</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.01331053257513998</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.03038637594154832</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.002872447233275045</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.02374861791700492</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8.593659866387402</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2455331390396401</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1194696359427715</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2044938832188407</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2865723948604394</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.336867563949472</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1810533589699849</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1124179194519061</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1424364525165428</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.219670265423427</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>35</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" t="n">
+        <v>35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.476941698767571</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.04219833425050203</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1723692874364632</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1014092561465263</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.04170743849372449</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0011916410998207</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.003640810982255645</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.002442303430185033</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>35</v>
+      </c>
+      <c r="D38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33.32071201701209</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9520203433432026</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1714656018470101</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8931198483083174</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D39" t="n">
+        <v>35</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.03595011794686365</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.001027146227053247</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.004848268842078485</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.00269258484438845</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1246887277797477</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.003562535079421364</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.009196932869635018</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0004032781031594697</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.006721792055683258</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1925494198538891</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.01604578498782409</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0417932503916747</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.04259994942171358</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.600949121822397</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1334124268185331</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1345144154626023</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.04794604472459575</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2188788089124705</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>35</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.866152750145967</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3221793958454973</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3260106147132888</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1150421335086453</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5293166581823492</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" t="n">
+        <v>35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0223463687150838</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.00186219739292365</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.00645084099653213</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.005960866219909941</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6.318002339462664</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.526500194955222</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3074581658893744</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3311505962268383</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7218497936836058</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>35</v>
+      </c>
+      <c r="D50" t="n">
+        <v>35</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2246105152868474</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.006417443293909924</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.01580863985655561</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0009869855032555094</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.01184790108456434</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>35</v>
+      </c>
+      <c r="D51" t="n">
+        <v>35</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.05611390050749318</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.001603254300214091</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.007570218945752143</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.004203715492570989</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>35</v>
+      </c>
+      <c r="D52" t="n">
+        <v>35</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.002333722287047841</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.667777962993831e-05</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0003944710640506496</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0002021833311763773</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>35</v>
+      </c>
+      <c r="D53" t="n">
+        <v>35</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4.52442803784338</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1292693725098109</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.06870413705015789</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1056686756959416</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1528700693236801</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>35</v>
+      </c>
+      <c r="D54" t="n">
+        <v>35</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5554703759652814</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.01587058217043661</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.07133730416846404</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.04037580353679422</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>35</v>
+      </c>
+      <c r="D55" t="n">
+        <v>35</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.03772160990539217</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.001077760283011205</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.002949459765889336</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6.458540463901482e-05</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.002090935161383395</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>35</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35</v>
+      </c>
+      <c r="E56" t="n">
+        <v>25.77018963951131</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.736291132557466</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1571073443620705</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6823228715368168</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7902593935781153</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>35</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.829132198693248</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.1094037771055214</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.08280447193463432</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.08095944579057969</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.137848108420463</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>35</v>
+      </c>
+      <c r="D58" t="n">
+        <v>35</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.0261897687108689</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0007482791060248258</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.002214444946988066</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.00150896756015264</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>35</v>
+      </c>
+      <c r="D59" t="n">
+        <v>35</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.001724137931034483</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.926108374384236e-05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.000291432501630523</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0001493716507053063</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>35</v>
+      </c>
+      <c r="D60" t="n">
+        <v>35</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.1526215916727</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.004360616904934285</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.007826886565055469</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.001671987300525387</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.007049246509343183</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>35</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.001002406045366</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.0571714973155819</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.04296968510908328</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.04241089403915116</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.07193210059201263</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>35</v>
+      </c>
+      <c r="D62" t="n">
+        <v>35</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.2396517333403195</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.006847192381151987</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.007058043441163824</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.004422669630325251</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.009271715131978723</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>35</v>
+      </c>
+      <c r="D63" t="n">
+        <v>35</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7092700482545649</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.020264858521559</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.084454092737307</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.04927585440858177</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>35</v>
+      </c>
+      <c r="D64" t="n">
+        <v>35</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7238555723144505</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02068158778041287</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.02736979736923796</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.01127973343360921</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.03008344212721653</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>35</v>
+      </c>
+      <c r="D65" t="n">
+        <v>35</v>
+      </c>
+      <c r="E65" t="n">
+        <v>31.1456847417307</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8898767069065914</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.1291474622434781</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8455130014362241</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9342404123769587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/lendt_adults.xlsx
+++ b/results/lendt_adults.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,20 +442,30 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>stairs</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bicycle</t>
         </is>
@@ -469,42 +479,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.98 [0.97, 0.99]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
     </row>
@@ -532,16 +552,22 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.99 [0.98, 1.00]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+          <t>0.93 [0.89, 0.97]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.82 [0.71, 0.92]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
@@ -555,42 +581,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.97 [0.96, 0.99]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.97 [0.96, 0.99]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
     </row>
@@ -618,16 +654,22 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.94 [0.91, 0.97]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.93 [0.86, 1.00]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.00 [1.00, 1.00]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
@@ -657,16 +699,22 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 1.00]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+          <t>0.95 [0.90, 1.00]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.78 [0.67, 0.89]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
@@ -696,16 +744,22 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>540.03 ± 0.17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+          <t>360.03 ± 0.17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>180.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>534.91 ± 30.44</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>539.69 ± 2.58</t>
         </is>
@@ -730,15 +784,21 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>18901</v>
+        <v>12601</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>18722</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>18889</v>
       </c>
     </row>
@@ -764,12 +824,18 @@
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" t="n">
         <v>35</v>
       </c>
     </row>
@@ -801,6 +867,12 @@
         <v>35</v>
       </c>
       <c r="I10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35</v>
+      </c>
+      <c r="K10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -815,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,7 +978,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -939,7 +1011,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -972,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1005,7 +1077,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1038,7 +1110,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1071,7 +1143,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1104,7 +1176,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1132,12 +1204,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1165,12 +1237,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1180,19 +1252,19 @@
         <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1203,7 +1275,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1236,7 +1308,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1269,7 +1341,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1279,19 +1351,19 @@
         <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1302,7 +1374,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1335,7 +1407,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1368,7 +1440,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1396,12 +1468,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1429,12 +1501,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1462,12 +1534,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1477,30 +1549,30 @@
         <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>34.90925925925926</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9974074074074074</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009728833730787922</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9940654360925615</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1510,19 +1582,19 @@
         <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0004761904761904762</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00157793689443717</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001018230764242453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1533,7 +1605,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1566,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1576,19 +1648,19 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.001904761904761905</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.007628584048087617</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.004525272211246011</v>
       </c>
     </row>
     <row r="24">
@@ -1599,7 +1671,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1632,7 +1704,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1642,30 +1714,30 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07407407407407408</v>
+        <v>34.91111111111111</v>
       </c>
       <c r="F25" t="n">
-        <v>0.002116402116402117</v>
+        <v>0.9974603174603175</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008582487592005968</v>
+        <v>0.009443544259352491</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.9942163465077295</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005064589754940576</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1675,30 +1747,30 @@
         <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.0006349206349206349</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.002151322552303417</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.001373925787822641</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>sit</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>lie</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1726,12 +1798,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1759,12 +1831,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1792,12 +1864,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1807,30 +1879,30 @@
         <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1863,7 +1935,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1896,7 +1968,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1924,12 +1996,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1957,12 +2029,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1990,12 +2062,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2023,12 +2095,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2038,30 +2110,30 @@
         <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3933333333333333</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01123809523809524</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01437330755676584</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.006300691343303916</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01617549913288656</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2089,7 +2161,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2122,14 +2194,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
       <c r="C40" t="n">
         <v>35</v>
       </c>
@@ -2137,25 +2209,25 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>34.60666666666667</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9887619047619048</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01437330755676583</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9838245008671135</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9936993086566962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2188,7 +2260,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2221,12 +2293,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2236,30 +2308,30 @@
         <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.00119047619047619</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.004583492485141057</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.002764960946925273</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2269,30 +2341,30 @@
         <v>35</v>
       </c>
       <c r="E44" t="n">
-        <v>0.001851851851851852</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>5.291005291005291e-05</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0003130200943438951</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0001604362174242179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2302,30 +2374,30 @@
         <v>35</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3185185185185185</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0091005291005291</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01895121625940376</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.002590558545688552</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01561049965536965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2335,30 +2407,30 @@
         <v>35</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.01388888888888889</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.0295742606297056</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.003729774917244471</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.0240480028605333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2368,30 +2440,30 @@
         <v>35</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.006349206349206349</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0375624113212674</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01925234609090615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2401,52 +2473,778 @@
         <v>35</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>33.21666666666667</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.9490476190476191</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.1420137726035333</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.9002641813317377</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.9978310567635006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.01238095238095238</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.07324670207647144</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.03754207487726699</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>35</v>
+      </c>
+      <c r="D50" t="n">
+        <v>35</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C51" t="n">
+        <v>35</v>
+      </c>
+      <c r="D51" t="n">
+        <v>35</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8222222222222223</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.02349206349206349</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.07835437202159054</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.0504077320022821</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>35</v>
+      </c>
+      <c r="D52" t="n">
+        <v>35</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>35</v>
+      </c>
+      <c r="D53" t="n">
+        <v>35</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>35</v>
+      </c>
+      <c r="D54" t="n">
+        <v>35</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>35</v>
+      </c>
+      <c r="D55" t="n">
+        <v>35</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>35</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3933333333333333</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.01123809523809524</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.01437330755676584</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.006300691343303916</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.01617549913288656</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>35</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>35</v>
+      </c>
+      <c r="D58" t="n">
+        <v>35</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>35</v>
+      </c>
+      <c r="D59" t="n">
+        <v>35</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>35</v>
+      </c>
+      <c r="D60" t="n">
+        <v>35</v>
+      </c>
+      <c r="E60" t="n">
+        <v>34.60666666666667</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.9887619047619048</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.01437330755676583</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9838245008671135</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9936993086566962</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>35</v>
-      </c>
-      <c r="D49" t="n">
-        <v>35</v>
-      </c>
-      <c r="E49" t="n">
-        <v>34.45740740740741</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.9844973544973545</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.05186952257698719</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.9666795500858688</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
+      <c r="C61" t="n">
+        <v>35</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>35</v>
+      </c>
+      <c r="D62" t="n">
+        <v>35</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>35</v>
+      </c>
+      <c r="D63" t="n">
+        <v>35</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.04523809523809524</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.1532280521929192</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.09787377277443815</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>35</v>
+      </c>
+      <c r="D64" t="n">
+        <v>35</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>35</v>
+      </c>
+      <c r="D65" t="n">
+        <v>35</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>35</v>
+      </c>
+      <c r="D66" t="n">
+        <v>35</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.005238095238095238</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0220969860433128</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.01282867552189676</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>35</v>
+      </c>
+      <c r="D67" t="n">
+        <v>35</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>35</v>
+      </c>
+      <c r="D68" t="n">
+        <v>35</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.1528571428571429</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.2706315116252214</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.05989196596418452</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.2458223197501012</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>35</v>
+      </c>
+      <c r="D69" t="n">
+        <v>35</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.01380952380952381</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.08169824462375661</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.04187385274772087</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>35</v>
+      </c>
+      <c r="D70" t="n">
+        <v>35</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>35</v>
+      </c>
+      <c r="D71" t="n">
+        <v>35</v>
+      </c>
+      <c r="E71" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7828571428571429</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.3216141756435709</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6723788081265131</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8933354775877728</v>
       </c>
     </row>
   </sheetData>
@@ -2513,42 +3311,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.92]</t>
+          <t>0.88 [0.84, 0.92]</t>
         </is>
       </c>
     </row>
@@ -2580,12 +3378,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.93]</t>
+          <t>0.89 [0.86, 0.92]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.35 [0.14, 0.56]</t>
+          <t>0.40 [0.18, 0.63]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2607,42 +3405,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.84 [0.80, 0.88]</t>
+          <t>0.83 [0.79, 0.88]</t>
         </is>
       </c>
     </row>
@@ -2669,17 +3467,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.40 [0.33, 0.47]</t>
+          <t>0.40 [0.32, 0.47]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.90 [0.87, 0.93]</t>
+          <t>0.90 [0.88, 0.93]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.70 [0.40, 0.99]</t>
+          <t>0.61 [0.34, 0.89]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2716,17 +3514,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.53 [0.47, 0.58]</t>
+          <t>0.53 [0.48, 0.59]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.89 [0.85, 0.93]</t>
+          <t>0.89 [0.85, 0.92]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.32 [0.12, 0.53]</t>
+          <t>0.39 [0.16, 0.61]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2959,19 +3757,19 @@
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>25.79294209144394</v>
+        <v>25.79394116727066</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9552941515349608</v>
+        <v>0.9553311543433578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04935390029809637</v>
+        <v>0.04949760198309867</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9357703988191506</v>
+        <v>0.9357505551342434</v>
       </c>
       <c r="I2" t="n">
-        <v>0.974817904250771</v>
+        <v>0.9749117535524722</v>
       </c>
     </row>
     <row r="3">
@@ -3058,19 +3856,19 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2867880116921117</v>
+        <v>0.3041740849368775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01062177821081895</v>
+        <v>0.01126570684951398</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01527115325376229</v>
+        <v>0.01527499508840483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004580711182461005</v>
+        <v>0.005223120041987966</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0166628452391769</v>
+        <v>0.01730829365703999</v>
       </c>
     </row>
     <row r="6">
@@ -3124,19 +3922,19 @@
         <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2305299170812718</v>
+        <v>0.2034790547998403</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00853814507708414</v>
+        <v>0.007536261288882975</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01359679625949877</v>
+        <v>0.01283083847797267</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003159431615851446</v>
+        <v>0.002460550634458701</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01391685853831683</v>
+        <v>0.01261197194330725</v>
       </c>
     </row>
     <row r="8">
@@ -3157,19 +3955,19 @@
         <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2425087082947844</v>
+        <v>0.2423752812902479</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008981804010917941</v>
+        <v>0.008976862270009182</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01869575412318582</v>
+        <v>0.01849769533145849</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001586009998043382</v>
+        <v>0.001659417705699395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0163775980237925</v>
+        <v>0.01629430683431897</v>
       </c>
     </row>
     <row r="9">
@@ -3190,19 +3988,19 @@
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1507013674285818</v>
+        <v>0.1595005076430634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005581532126984512</v>
+        <v>0.005907426209002348</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008919456752059171</v>
+        <v>0.009688662152191222</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00205311255052231</v>
+        <v>0.002074719110598882</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009109951703446712</v>
+        <v>0.009740133307405814</v>
       </c>
     </row>
     <row r="10">
@@ -3553,19 +4351,19 @@
         <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>23.31858924947201</v>
+        <v>23.19872187160048</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9716078853946669</v>
+        <v>0.9666134113166865</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0683508983184844</v>
+        <v>0.07226472661573935</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9427458323074687</v>
+        <v>0.9360986934823009</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.9971281291510722</v>
       </c>
     </row>
     <row r="21">
@@ -3586,19 +4384,19 @@
         <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09415630070552564</v>
+        <v>0.05906858140728002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003923179196063568</v>
+        <v>0.002461190891970001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01005499132451292</v>
+        <v>0.007570625447487242</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008169029660927578</v>
+        <v>0.005657985651719046</v>
       </c>
     </row>
     <row r="22">
@@ -3718,19 +4516,19 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5443345917989302</v>
+        <v>0.6992896889687081</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02268060799162209</v>
+        <v>0.02913707037369617</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0556586835531665</v>
+        <v>0.05977803795123855</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.003895018736598463</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04618320882050729</v>
+        <v>0.05437912201079388</v>
       </c>
     </row>
     <row r="26">
@@ -3850,19 +4648,19 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>18.43957851859527</v>
+        <v>18.67226968705118</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5268451005312933</v>
+        <v>0.5334934196300336</v>
       </c>
       <c r="G29" t="n">
-        <v>0.165324306370006</v>
+        <v>0.1668775175544746</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4700542143033907</v>
+        <v>0.4761689866926251</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5836359867591959</v>
+        <v>0.5908178525674421</v>
       </c>
     </row>
     <row r="30">
@@ -3916,19 +4714,19 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4658686401298994</v>
+        <v>0.4780411723636627</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01331053257513998</v>
+        <v>0.01365831921039036</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03038637594154832</v>
+        <v>0.0309857185314132</v>
       </c>
       <c r="H31" t="n">
-        <v>0.002872447233275045</v>
+        <v>0.003014352485564253</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02374861791700492</v>
+        <v>0.02430228593521647</v>
       </c>
     </row>
     <row r="32">
@@ -3949,19 +4747,19 @@
         <v>35</v>
       </c>
       <c r="E32" t="n">
-        <v>8.593659866387402</v>
+        <v>8.563823858628629</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2455331390396401</v>
+        <v>0.2446806816751037</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1194696359427715</v>
+        <v>0.120332415355607</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2044938832188407</v>
+        <v>0.2033450507564742</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2865723948604394</v>
+        <v>0.2860163125937332</v>
       </c>
     </row>
     <row r="33">
@@ -3982,19 +4780,19 @@
         <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>6.336867563949472</v>
+        <v>6.121839871018567</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1810533589699849</v>
+        <v>0.1749097106005305</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1124179194519061</v>
+        <v>0.1073124484175371</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1424364525165428</v>
+        <v>0.1380465948087216</v>
       </c>
       <c r="I33" t="n">
-        <v>0.219670265423427</v>
+        <v>0.2117728263923394</v>
       </c>
     </row>
     <row r="34">
@@ -4114,19 +4912,19 @@
         <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>0.04170743849372449</v>
+        <v>0.04038585259064079</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0011916410998207</v>
+        <v>0.001153881502589737</v>
       </c>
       <c r="G37" t="n">
-        <v>0.003640810982255645</v>
+        <v>0.00364627278269086</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.002442303430185033</v>
+        <v>0.002406420027047524</v>
       </c>
     </row>
     <row r="38">
@@ -4246,19 +5044,19 @@
         <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1246887277797477</v>
+        <v>0.1260103136828314</v>
       </c>
       <c r="F41" t="n">
-        <v>0.003562535079421364</v>
+        <v>0.003600294676652327</v>
       </c>
       <c r="G41" t="n">
-        <v>0.009196932869635018</v>
+        <v>0.009184580776815559</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0004032781031594697</v>
+        <v>0.0004452807927305055</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006721792055683258</v>
+        <v>0.006755308560574149</v>
       </c>
     </row>
     <row r="42">
@@ -4378,19 +5176,19 @@
         <v>35</v>
       </c>
       <c r="E45" t="n">
-        <v>1.600949121822397</v>
+        <v>1.486471501462668</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1334124268185331</v>
+        <v>0.123872625121889</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1345144154626023</v>
+        <v>0.1347143127588792</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04794604472459575</v>
+        <v>0.03827923434531788</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2188788089124705</v>
+        <v>0.2094660158984601</v>
       </c>
     </row>
     <row r="46">
@@ -4444,19 +5242,19 @@
         <v>35</v>
       </c>
       <c r="E47" t="n">
-        <v>3.866152750145967</v>
+        <v>4.624743649920511</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3221793958454973</v>
+        <v>0.3853953041600426</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3260106147132888</v>
+        <v>0.3491988043836182</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1150421335086453</v>
+        <v>0.1635249690025899</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5293166581823492</v>
+        <v>0.6072656393174953</v>
       </c>
     </row>
     <row r="48">
@@ -4510,19 +5308,19 @@
         <v>35</v>
       </c>
       <c r="E49" t="n">
-        <v>6.318002339462664</v>
+        <v>5.673889060047848</v>
       </c>
       <c r="F49" t="n">
-        <v>0.526500194955222</v>
+        <v>0.4728240883373207</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3074581658893744</v>
+        <v>0.3313036123405337</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3311505962268383</v>
+        <v>0.2623238157530043</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7218497936836058</v>
+        <v>0.6833243609216371</v>
       </c>
     </row>
     <row r="50">
@@ -4642,19 +5440,19 @@
         <v>35</v>
       </c>
       <c r="E53" t="n">
-        <v>4.52442803784338</v>
+        <v>4.55986053203689</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1292693725098109</v>
+        <v>0.1302817294867683</v>
       </c>
       <c r="G53" t="n">
-        <v>0.06870413705015789</v>
+        <v>0.07049698154634382</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1056686756959416</v>
+        <v>0.1060651690407278</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1528700693236801</v>
+        <v>0.1544982899328087</v>
       </c>
     </row>
     <row r="54">
@@ -4708,19 +5506,19 @@
         <v>35</v>
       </c>
       <c r="E55" t="n">
-        <v>0.03772160990539217</v>
+        <v>0.04208150457309086</v>
       </c>
       <c r="F55" t="n">
-        <v>0.001077760283011205</v>
+        <v>0.00120232870208831</v>
       </c>
       <c r="G55" t="n">
-        <v>0.002949459765889336</v>
+        <v>0.002948913488652961</v>
       </c>
       <c r="H55" t="n">
-        <v>6.458540463901482e-05</v>
+        <v>0.0001893414765123788</v>
       </c>
       <c r="I55" t="n">
-        <v>0.002090935161383395</v>
+        <v>0.002215315927664241</v>
       </c>
     </row>
     <row r="56">
@@ -4741,19 +5539,19 @@
         <v>35</v>
       </c>
       <c r="E56" t="n">
-        <v>25.77018963951131</v>
+        <v>25.77692398342126</v>
       </c>
       <c r="F56" t="n">
-        <v>0.736291132557466</v>
+        <v>0.7364835423834646</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1571073443620705</v>
+        <v>0.1574024404672463</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6823228715368168</v>
+        <v>0.6824139123040042</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7902593935781153</v>
+        <v>0.790553172462925</v>
       </c>
     </row>
     <row r="57">
@@ -4774,19 +5572,19 @@
         <v>35</v>
       </c>
       <c r="E57" t="n">
-        <v>3.829132198693248</v>
+        <v>3.782605465922092</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1094037771055214</v>
+        <v>0.1080744418834883</v>
       </c>
       <c r="G57" t="n">
-        <v>0.08280447193463432</v>
+        <v>0.08229925552764805</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08095944579057969</v>
+        <v>0.07980365847641094</v>
       </c>
       <c r="I57" t="n">
-        <v>0.137848108420463</v>
+        <v>0.1363452252905657</v>
       </c>
     </row>
     <row r="58">
@@ -4873,19 +5671,19 @@
         <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1526215916727</v>
+        <v>0.1473791098123975</v>
       </c>
       <c r="F60" t="n">
-        <v>0.004360616904934285</v>
+        <v>0.004210831708925643</v>
       </c>
       <c r="G60" t="n">
-        <v>0.007826886565055469</v>
+        <v>0.007856267315650032</v>
       </c>
       <c r="H60" t="n">
-        <v>0.001671987300525387</v>
+        <v>0.001512109463567919</v>
       </c>
       <c r="I60" t="n">
-        <v>0.007049246509343183</v>
+        <v>0.006909553954283366</v>
       </c>
     </row>
     <row r="61">
@@ -4906,19 +5704,19 @@
         <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>2.001002406045366</v>
+        <v>2.144841276100773</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0571714973155819</v>
+        <v>0.06128117931716494</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04296968510908328</v>
+        <v>0.04199212789101204</v>
       </c>
       <c r="H61" t="n">
-        <v>0.04241089403915116</v>
+        <v>0.04685637869414742</v>
       </c>
       <c r="I61" t="n">
-        <v>0.07193210059201263</v>
+        <v>0.07570597994018245</v>
       </c>
     </row>
     <row r="62">
@@ -4939,19 +5737,19 @@
         <v>35</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2396517333403195</v>
+        <v>0.2535500696982319</v>
       </c>
       <c r="F62" t="n">
-        <v>0.006847192381151987</v>
+        <v>0.007244287705663769</v>
       </c>
       <c r="G62" t="n">
-        <v>0.007058043441163824</v>
+        <v>0.007639814028838257</v>
       </c>
       <c r="H62" t="n">
-        <v>0.004422669630325251</v>
+        <v>0.004619919765821603</v>
       </c>
       <c r="I62" t="n">
-        <v>0.009271715131978723</v>
+        <v>0.009868655645505934</v>
       </c>
     </row>
     <row r="63">
@@ -4972,19 +5770,19 @@
         <v>35</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7092700482545649</v>
+        <v>0.6541834345535092</v>
       </c>
       <c r="F63" t="n">
-        <v>0.020264858521559</v>
+        <v>0.01869095527295741</v>
       </c>
       <c r="G63" t="n">
-        <v>0.084454092737307</v>
+        <v>0.07304340144484851</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.04927585440858177</v>
+        <v>0.04378224155889217</v>
       </c>
     </row>
     <row r="64">
@@ -5005,19 +5803,19 @@
         <v>35</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7238555723144505</v>
+        <v>0.7158155767203813</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02068158778041287</v>
+        <v>0.02045187362058232</v>
       </c>
       <c r="G64" t="n">
-        <v>0.02736979736923796</v>
+        <v>0.02759327646184083</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01127973343360921</v>
+        <v>0.01097325151953253</v>
       </c>
       <c r="I64" t="n">
-        <v>0.03008344212721653</v>
+        <v>0.02993049572163212</v>
       </c>
     </row>
     <row r="65">
@@ -5038,19 +5836,19 @@
         <v>35</v>
       </c>
       <c r="E65" t="n">
-        <v>31.1456847417307</v>
+        <v>31.0563166264728</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8898767069065914</v>
+        <v>0.8873233321849372</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1291474622434781</v>
+        <v>0.1094679179916101</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8455130014362241</v>
+        <v>0.8497197866884065</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9342404123769587</v>
+        <v>0.9249268776814679</v>
       </c>
     </row>
   </sheetData>
